--- a/data/QuestionTest.xlsx
+++ b/data/QuestionTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ardit\Desktop\New folder (2)\RAG\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA035F4A-F207-4410-B192-9A8FA4F1E2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE330C0-F61A-4F4A-AFFB-F78F849D1EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,9 +34,6 @@
     <t>IdentifiantsATrouver</t>
   </si>
   <si>
-    <t>quel évènement se sont produit le 25 août 2025 à Nice ?</t>
-  </si>
-  <si>
     <t>2 évènements se sont déroulé le 25 aout 2025 à Nice, le premier : comment mobiliser vos applications France Travail, le deuxième : atelier le héros aux mille et un visage avec Dany Albiach</t>
   </si>
   <si>
@@ -65,6 +62,9 @@
   </si>
   <si>
     <t>21312701</t>
+  </si>
+  <si>
+    <t>quels évènements se sont produit le 25 août 2025 à Nice ?</t>
   </si>
 </sst>
 </file>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -479,13 +479,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -493,13 +493,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -507,13 +507,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
